--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>657000</v>
+        <v>648000</v>
       </c>
       <c r="C419" t="n">
-        <v>51316</v>
+        <v>163642</v>
       </c>
       <c r="D419" t="n">
-        <v>641227</v>
+        <v>641288</v>
       </c>
       <c r="E419" t="n">
-        <v>663644</v>
+        <v>662727</v>
       </c>
       <c r="F419" t="n">
-        <v>663775</v>
+        <v>658720</v>
       </c>
       <c r="G419" t="n">
-        <v>656216</v>
+        <v>654245</v>
       </c>
       <c r="H419" t="n">
-        <v>0.4503741883009242</v>
+        <v>0.4460178673256034</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>0.4460178673256034</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>651000</v>
+      </c>
+      <c r="C420" t="n">
+        <v>46442</v>
+      </c>
+      <c r="D420" t="n">
+        <v>643447</v>
+      </c>
+      <c r="E420" t="n">
+        <v>665808</v>
+      </c>
+      <c r="F420" t="n">
+        <v>655456</v>
+      </c>
+      <c r="G420" t="n">
+        <v>654904</v>
+      </c>
+      <c r="H420" t="n">
+        <v>0.4474743947343993</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -11340,22 +11340,22 @@
         <v>655000</v>
       </c>
       <c r="C421" t="n">
-        <v>8455</v>
+        <v>94162</v>
       </c>
       <c r="D421" t="n">
-        <v>643704</v>
+        <v>643912</v>
       </c>
       <c r="E421" t="n">
-        <v>665767</v>
+        <v>665363</v>
       </c>
       <c r="F421" t="n">
-        <v>653641</v>
+        <v>653923</v>
       </c>
       <c r="G421" t="n">
-        <v>654371</v>
+        <v>654399</v>
       </c>
       <c r="H421" t="n">
-        <v>0.4462963535979985</v>
+        <v>0.4463582394363084</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>0.4463582394363084</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>648000</v>
+      </c>
+      <c r="C422" t="n">
+        <v>59471</v>
+      </c>
+      <c r="D422" t="n">
+        <v>644061</v>
+      </c>
+      <c r="E422" t="n">
+        <v>664923</v>
+      </c>
+      <c r="F422" t="n">
+        <v>652003</v>
+      </c>
+      <c r="G422" t="n">
+        <v>653662</v>
+      </c>
+      <c r="H422" t="n">
+        <v>0.4447293157636492</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>0.4447293157636492</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>661000</v>
+      </c>
+      <c r="C423" t="n">
+        <v>66029</v>
+      </c>
+      <c r="D423" t="n">
+        <v>645039</v>
+      </c>
+      <c r="E423" t="n">
+        <v>664129</v>
+      </c>
+      <c r="F423" t="n">
+        <v>651855</v>
+      </c>
+      <c r="G423" t="n">
+        <v>653674</v>
+      </c>
+      <c r="H423" t="n">
+        <v>0.4447558382657819</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>0.4447558382657819</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>653000</v>
+      </c>
+      <c r="C424" t="n">
+        <v>72915</v>
+      </c>
+      <c r="D424" t="n">
+        <v>648867</v>
+      </c>
+      <c r="E424" t="n">
+        <v>663724</v>
+      </c>
+      <c r="F424" t="n">
+        <v>653963</v>
+      </c>
+      <c r="G424" t="n">
+        <v>655518</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0.4488314627601968</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>0.4488314627601968</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>633000</v>
+      </c>
+      <c r="C425" t="n">
+        <v>70130</v>
+      </c>
+      <c r="D425" t="n">
+        <v>650497</v>
+      </c>
+      <c r="E425" t="n">
+        <v>662553</v>
+      </c>
+      <c r="F425" t="n">
+        <v>650289</v>
+      </c>
+      <c r="G425" t="n">
+        <v>654446</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0.4464621192363287</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>0.4464621192363287</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>626000</v>
+      </c>
+      <c r="C426" t="n">
+        <v>34255</v>
+      </c>
+      <c r="D426" t="n">
+        <v>650291</v>
+      </c>
+      <c r="E426" t="n">
+        <v>661393</v>
+      </c>
+      <c r="F426" t="n">
+        <v>646076</v>
+      </c>
+      <c r="G426" t="n">
+        <v>652587</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0.442353341614248</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>626000</v>
+      </c>
+      <c r="C427" t="n">
+        <v>41069</v>
+      </c>
+      <c r="D427" t="n">
+        <v>650048</v>
+      </c>
+      <c r="E427" t="n">
+        <v>660790</v>
+      </c>
+      <c r="F427" t="n">
+        <v>642774</v>
+      </c>
+      <c r="G427" t="n">
+        <v>651204</v>
+      </c>
+      <c r="H427" t="n">
+        <v>0.4392966232434368</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>0.4392966232434368</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>635000</v>
+      </c>
+      <c r="C428" t="n">
+        <v>83413</v>
+      </c>
+      <c r="D428" t="n">
+        <v>651216</v>
+      </c>
+      <c r="E428" t="n">
+        <v>653122</v>
+      </c>
+      <c r="F428" t="n">
+        <v>636638</v>
+      </c>
+      <c r="G428" t="n">
+        <v>646992</v>
+      </c>
+      <c r="H428" t="n">
+        <v>0.429987224994806</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>0.429987224994806</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>629000</v>
+      </c>
+      <c r="C429" t="n">
+        <v>67170</v>
+      </c>
+      <c r="D429" t="n">
+        <v>650974</v>
+      </c>
+      <c r="E429" t="n">
+        <v>651912</v>
+      </c>
+      <c r="F429" t="n">
+        <v>630875</v>
+      </c>
+      <c r="G429" t="n">
+        <v>644587</v>
+      </c>
+      <c r="H429" t="n">
+        <v>0.4246716735256804</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>0.4246716735256804</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>612000</v>
+      </c>
+      <c r="C430" t="n">
+        <v>119036</v>
+      </c>
+      <c r="D430" t="n">
+        <v>649808</v>
+      </c>
+      <c r="E430" t="n">
+        <v>649233</v>
+      </c>
+      <c r="F430" t="n">
+        <v>623929</v>
+      </c>
+      <c r="G430" t="n">
+        <v>640990</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0.4167215535113582</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>0.4167215535113582</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>622000</v>
+      </c>
+      <c r="C431" t="n">
+        <v>98168</v>
+      </c>
+      <c r="D431" t="n">
+        <v>650120</v>
+      </c>
+      <c r="E431" t="n">
+        <v>644022</v>
+      </c>
+      <c r="F431" t="n">
+        <v>623293</v>
+      </c>
+      <c r="G431" t="n">
+        <v>639145</v>
+      </c>
+      <c r="H431" t="n">
+        <v>0.4126437188084324</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>0.4126437188084324</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>612000</v>
+      </c>
+      <c r="C432" t="n">
+        <v>144819</v>
+      </c>
+      <c r="D432" t="n">
+        <v>650804</v>
+      </c>
+      <c r="E432" t="n">
+        <v>640799</v>
+      </c>
+      <c r="F432" t="n">
+        <v>619885</v>
+      </c>
+      <c r="G432" t="n">
+        <v>637163</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0.4082630855394898</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>0.4082630855394898</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>582000</v>
+      </c>
+      <c r="C433" t="n">
+        <v>118151</v>
+      </c>
+      <c r="D433" t="n">
+        <v>650429</v>
+      </c>
+      <c r="E433" t="n">
+        <v>634702</v>
+      </c>
+      <c r="F433" t="n">
+        <v>609404</v>
+      </c>
+      <c r="G433" t="n">
+        <v>631512</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0.395773197243428</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>0.395773197243428</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>580000</v>
+      </c>
+      <c r="C434" t="n">
+        <v>123454</v>
+      </c>
+      <c r="D434" t="n">
+        <v>648158</v>
+      </c>
+      <c r="E434" t="n">
+        <v>628379</v>
+      </c>
+      <c r="F434" t="n">
+        <v>601210</v>
+      </c>
+      <c r="G434" t="n">
+        <v>625916</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0.3834048704154749</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>0.3834048704154749</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>586000</v>
+      </c>
+      <c r="C435" t="n">
+        <v>86207</v>
+      </c>
+      <c r="D435" t="n">
+        <v>646790</v>
+      </c>
+      <c r="E435" t="n">
+        <v>624691</v>
+      </c>
+      <c r="F435" t="n">
+        <v>596662</v>
+      </c>
+      <c r="G435" t="n">
+        <v>622714</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0.3763277827630258</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>0.3763277827630258</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>607000</v>
+      </c>
+      <c r="C436" t="n">
+        <v>64869</v>
+      </c>
+      <c r="D436" t="n">
+        <v>647813</v>
+      </c>
+      <c r="E436" t="n">
+        <v>619724</v>
+      </c>
+      <c r="F436" t="n">
+        <v>593282</v>
+      </c>
+      <c r="G436" t="n">
+        <v>620273</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0.3709326637875017</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>0.3709326637875017</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>602000</v>
+      </c>
+      <c r="C437" t="n">
+        <v>83567</v>
+      </c>
+      <c r="D437" t="n">
+        <v>647280</v>
+      </c>
+      <c r="E437" t="n">
+        <v>618719</v>
+      </c>
+      <c r="F437" t="n">
+        <v>589120</v>
+      </c>
+      <c r="G437" t="n">
+        <v>618373</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0.366733267616467</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>0.366733267616467</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>601000</v>
+      </c>
+      <c r="C438" t="n">
+        <v>72911</v>
+      </c>
+      <c r="D438" t="n">
+        <v>645932</v>
+      </c>
+      <c r="E438" t="n">
+        <v>616858</v>
+      </c>
+      <c r="F438" t="n">
+        <v>593082</v>
+      </c>
+      <c r="G438" t="n">
+        <v>618624</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0.3672880299527457</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>0.3672880299527457</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>608000</v>
+      </c>
+      <c r="C439" t="n">
+        <v>81456</v>
+      </c>
+      <c r="D439" t="n">
+        <v>645113</v>
+      </c>
+      <c r="E439" t="n">
+        <v>613957</v>
+      </c>
+      <c r="F439" t="n">
+        <v>600357</v>
+      </c>
+      <c r="G439" t="n">
+        <v>619809</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0.3699071270383647</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>0.3699071270383647</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>602000</v>
+      </c>
+      <c r="C440" t="n">
+        <v>84815</v>
+      </c>
+      <c r="D440" t="n">
+        <v>644166</v>
+      </c>
+      <c r="E440" t="n">
+        <v>611948</v>
+      </c>
+      <c r="F440" t="n">
+        <v>603910</v>
+      </c>
+      <c r="G440" t="n">
+        <v>620008</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0.370346958532068</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>0.370346958532068</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>595000</v>
+      </c>
+      <c r="C441" t="n">
+        <v>61009</v>
+      </c>
+      <c r="D441" t="n">
+        <v>642661</v>
+      </c>
+      <c r="E441" t="n">
+        <v>611291</v>
+      </c>
+      <c r="F441" t="n">
+        <v>601971</v>
+      </c>
+      <c r="G441" t="n">
+        <v>618641</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0.3673256034974339</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>0.3673256034974339</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>597000</v>
+      </c>
+      <c r="C442" t="n">
+        <v>106687</v>
+      </c>
+      <c r="D442" t="n">
+        <v>640547</v>
+      </c>
+      <c r="E442" t="n">
+        <v>610384</v>
+      </c>
+      <c r="F442" t="n">
+        <v>600661</v>
+      </c>
+      <c r="G442" t="n">
+        <v>617197</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0.3641340624074476</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>0.3641340624074476</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>637000</v>
+      </c>
+      <c r="C443" t="n">
+        <v>106224</v>
+      </c>
+      <c r="D443" t="n">
+        <v>638674</v>
+      </c>
+      <c r="E443" t="n">
+        <v>610084</v>
+      </c>
+      <c r="F443" t="n">
+        <v>609374</v>
+      </c>
+      <c r="G443" t="n">
+        <v>619378</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0.3689545271700931</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>0.3689545271700931</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>651000</v>
+      </c>
+      <c r="C444" t="n">
+        <v>126997</v>
+      </c>
+      <c r="D444" t="n">
+        <v>639088</v>
+      </c>
+      <c r="E444" t="n">
+        <v>611249</v>
+      </c>
+      <c r="F444" t="n">
+        <v>620488</v>
+      </c>
+      <c r="G444" t="n">
+        <v>623608</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0.3783037091719232</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성화재_일별_기준주가.xlsx
+++ b/data/삼성화재_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>0.3783037091719232</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>659000</v>
+      </c>
+      <c r="C445" t="n">
+        <v>95870</v>
+      </c>
+      <c r="D445" t="n">
+        <v>639581</v>
+      </c>
+      <c r="E445" t="n">
+        <v>612945</v>
+      </c>
+      <c r="F445" t="n">
+        <v>631076</v>
+      </c>
+      <c r="G445" t="n">
+        <v>627867</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0.3877169872205743</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
